--- a/src/src/main/webapp/portal/asset/qrCode/QRCodeImportTemplate.xlsx
+++ b/src/src/main/webapp/portal/asset/qrCode/QRCodeImportTemplate.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{5A1D4A31-920F-4505-9418-DD6784413A3B}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{99EB20B9-0AC8-48D2-8CB1-1D60DF94BC3E}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="datelist" sheetId="1" r:id="rId1"/>
+    <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,33 +21,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>二维码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>填写说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、直接在datelist中输入要导入的二维码值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、输入的二维码值不可以超过16位字符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、输入的二维码值不可以在要导入的院区中重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、输入的二维码值导入后不可以更改所属院区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,12 +112,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -341,17 +418,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E29662-B39B-40B6-8E04-E82F988AC6A8}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="80.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/src/main/webapp/portal/asset/qrCode/QRCodeImportTemplate.xlsx
+++ b/src/src/main/webapp/portal/asset/qrCode/QRCodeImportTemplate.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{99EB20B9-0AC8-48D2-8CB1-1D60DF94BC3E}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960FDDAE-28C5-40EF-9AC2-2E8F2C18AFDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,17 +51,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -84,7 +84,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -131,12 +131,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,12 +419,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.25" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -431,38 +432,39 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76E29662-B39B-40B6-8E04-E82F988AC6A8}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="80.625" customWidth="1"/>
+    <col min="1" max="1" width="80.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>5</v>
       </c>

--- a/src/src/main/webapp/portal/asset/qrCode/QRCodeImportTemplate.xlsx
+++ b/src/src/main/webapp/portal/asset/qrCode/QRCodeImportTemplate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960FDDAE-28C5-40EF-9AC2-2E8F2C18AFDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A448B74E-D085-4A64-A388-2FCAB73FBA50}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,16 +35,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2、输入的二维码值不可以超过16位字符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3、输入的二维码值不可以在要导入的院区中重复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4、输入的二维码值导入后不可以更改所属院区</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、输入的二维码值不可以超过64位字符</t>
   </si>
 </sst>
 </file>
@@ -456,17 +455,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
